--- a/xy10102/output/prediction_results.xlsx
+++ b/xy10102/output/prediction_results.xlsx
@@ -405,13 +405,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>84.96333333333332</v>
+        <v>78.25666666666667</v>
       </c>
       <c r="C2">
-        <v>81.66020479932105</v>
+        <v>78.01791290383363</v>
       </c>
       <c r="D2">
-        <v>3.303128534012274</v>
+        <v>0.2387537628330421</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -419,13 +419,13 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>71.32666666666667</v>
+        <v>93.95</v>
       </c>
       <c r="C3">
-        <v>77.48652957010579</v>
+        <v>91.2901207852333</v>
       </c>
       <c r="D3">
-        <v>-6.159862903439119</v>
+        <v>2.659879214766704</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -433,13 +433,13 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>43.37</v>
+        <v>71.32666666666667</v>
       </c>
       <c r="C4">
-        <v>44.16703548089536</v>
+        <v>83.46055311405463</v>
       </c>
       <c r="D4">
-        <v>-0.797035480895353</v>
+        <v>-12.13388644738797</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -447,13 +447,13 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>36.68</v>
+        <v>43.37</v>
       </c>
       <c r="C5">
-        <v>41.80892853698196</v>
+        <v>44.42996893588631</v>
       </c>
       <c r="D5">
-        <v>-5.128928536981959</v>
+        <v>-1.05996893588631</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -461,13 +461,13 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>30.605</v>
+        <v>36.68</v>
       </c>
       <c r="C6">
-        <v>35.43100820359587</v>
+        <v>38.1193630914926</v>
       </c>
       <c r="D6">
-        <v>-4.826008203595872</v>
+        <v>-1.439363091492602</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -475,13 +475,13 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>40.965</v>
+        <v>30.605</v>
       </c>
       <c r="C7">
-        <v>40.56184229055896</v>
+        <v>32.53949500236358</v>
       </c>
       <c r="D7">
-        <v>0.4031577094410395</v>
+        <v>-1.93449500236358</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -489,13 +489,13 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>43.17</v>
+        <v>40.965</v>
       </c>
       <c r="C8">
-        <v>38.9784167310338</v>
+        <v>33.00218247168187</v>
       </c>
       <c r="D8">
-        <v>4.191583268966205</v>
+        <v>7.962817528318133</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -503,13 +503,13 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>54.42</v>
+        <v>43.17</v>
       </c>
       <c r="C9">
-        <v>48.49726069433684</v>
+        <v>37.29913932109955</v>
       </c>
       <c r="D9">
-        <v>5.922739305663157</v>
+        <v>5.870860678900456</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -517,13 +517,13 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>112.45</v>
+        <v>54.42</v>
       </c>
       <c r="C10">
-        <v>110.6503217221935</v>
+        <v>48.89442228504696</v>
       </c>
       <c r="D10">
-        <v>1.799678277806507</v>
+        <v>5.525577714953045</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -531,13 +531,13 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>112.16</v>
+        <v>112.45</v>
       </c>
       <c r="C11">
-        <v>103.5767831884667</v>
+        <v>110.8771089490875</v>
       </c>
       <c r="D11">
-        <v>8.583216811533262</v>
+        <v>1.572891050912546</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -545,13 +545,13 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>105.1466666666667</v>
+        <v>112.16</v>
       </c>
       <c r="C12">
-        <v>107.3510130585781</v>
+        <v>104.9877293624945</v>
       </c>
       <c r="D12">
-        <v>-2.204346391911443</v>
+        <v>7.172270637505548</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -559,13 +559,13 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>100.8366666666667</v>
+        <v>105.1466666666667</v>
       </c>
       <c r="C13">
-        <v>106.0134170275181</v>
+        <v>108.125826519819</v>
       </c>
       <c r="D13">
-        <v>-5.176750360851401</v>
+        <v>-2.979159853152325</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -573,13 +573,13 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>82.01333333333334</v>
+        <v>100.8366666666667</v>
       </c>
       <c r="C14">
-        <v>91.11846769286986</v>
+        <v>106.0967290035611</v>
       </c>
       <c r="D14">
-        <v>-9.105134359536521</v>
+        <v>-5.260062336894464</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -587,13 +587,13 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>89.33666666666666</v>
+        <v>82.01333333333334</v>
       </c>
       <c r="C15">
-        <v>98.34784668155913</v>
+        <v>92.42962020595127</v>
       </c>
       <c r="D15">
-        <v>-9.011180014892474</v>
+        <v>-10.41628687261793</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -601,13 +601,13 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>49.69333333333334</v>
+        <v>89.33666666666666</v>
       </c>
       <c r="C16">
-        <v>49.60356496521683</v>
+        <v>98.09468660156361</v>
       </c>
       <c r="D16">
-        <v>0.08976836811650912</v>
+        <v>-8.75801993489695</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -615,13 +615,13 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>8.765000000000001</v>
+        <v>41.13500000000001</v>
       </c>
       <c r="C17">
-        <v>8.640887951386809</v>
+        <v>41.84856867909997</v>
       </c>
       <c r="D17">
-        <v>0.1241120486131919</v>
+        <v>-0.7135686790999642</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -629,13 +629,13 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>12.29666666666667</v>
+        <v>8.765000000000001</v>
       </c>
       <c r="C18">
-        <v>11.07392643214438</v>
+        <v>8.732104829467682</v>
       </c>
       <c r="D18">
-        <v>1.222740234522288</v>
+        <v>0.03289517053231883</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -643,13 +643,13 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>11.39</v>
+        <v>12.29666666666667</v>
       </c>
       <c r="C19">
-        <v>10.07713623590903</v>
+        <v>10.93028668704606</v>
       </c>
       <c r="D19">
-        <v>1.31286376409097</v>
+        <v>1.366379979620604</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -657,13 +657,13 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>9.42</v>
+        <v>11.39</v>
       </c>
       <c r="C20">
-        <v>10.55306455875001</v>
+        <v>10.45926905224792</v>
       </c>
       <c r="D20">
-        <v>-1.133064558750007</v>
+        <v>0.9307309477520835</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -671,13 +671,13 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>24.63</v>
+        <v>9.42</v>
       </c>
       <c r="C21">
-        <v>11.35138741543368</v>
+        <v>10.71614745952499</v>
       </c>
       <c r="D21">
-        <v>13.27861258456632</v>
+        <v>-1.296147459524992</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -685,13 +685,13 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>14.005</v>
+        <v>24.63</v>
       </c>
       <c r="C22">
-        <v>10.62903695905527</v>
+        <v>11.58471290640559</v>
       </c>
       <c r="D22">
-        <v>3.375963040944731</v>
+        <v>13.04528709359441</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -699,13 +699,13 @@
         <v>21</v>
       </c>
       <c r="B23">
-        <v>28.43</v>
+        <v>14.005</v>
       </c>
       <c r="C23">
-        <v>32.9616029334202</v>
+        <v>11.27055579359363</v>
       </c>
       <c r="D23">
-        <v>-4.531602933420203</v>
+        <v>2.734444206406373</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -713,13 +713,13 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>79.94</v>
+        <v>28.43</v>
       </c>
       <c r="C24">
-        <v>79.97961367204962</v>
+        <v>31.10703738168999</v>
       </c>
       <c r="D24">
-        <v>-0.03961367204962585</v>
+        <v>-2.677037381689992</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -727,13 +727,13 @@
         <v>23</v>
       </c>
       <c r="B25">
-        <v>71.31666666666666</v>
+        <v>79.94</v>
       </c>
       <c r="C25">
-        <v>79.38291543130889</v>
+        <v>79.38925782072234</v>
       </c>
       <c r="D25">
-        <v>-8.066248764642225</v>
+        <v>0.5507421792776626</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -741,13 +741,13 @@
         <v>24</v>
       </c>
       <c r="B26">
-        <v>69.16666666666667</v>
+        <v>71.31666666666666</v>
       </c>
       <c r="C26">
-        <v>74.76533045431421</v>
+        <v>78.52865407044482</v>
       </c>
       <c r="D26">
-        <v>-5.598663787647538</v>
+        <v>-7.211987403778153</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -755,13 +755,13 @@
         <v>25</v>
       </c>
       <c r="B27">
-        <v>59.31999999999999</v>
+        <v>75.55500000000001</v>
       </c>
       <c r="C27">
-        <v>58.2726568452381</v>
+        <v>73.85303163720542</v>
       </c>
       <c r="D27">
-        <v>1.047343154761897</v>
+        <v>1.701968362794588</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -769,13 +769,13 @@
         <v>26</v>
       </c>
       <c r="B28">
-        <v>57.33666666666667</v>
+        <v>59.31999999999999</v>
       </c>
       <c r="C28">
-        <v>60.83266792989418</v>
+        <v>58.57816685846563</v>
       </c>
       <c r="D28">
-        <v>-3.496001263227512</v>
+        <v>0.7418331415343644</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -783,13 +783,13 @@
         <v>27</v>
       </c>
       <c r="B29">
-        <v>35.85333333333333</v>
+        <v>57.33666666666667</v>
       </c>
       <c r="C29">
-        <v>41.24414387578427</v>
+        <v>61.03168287698414</v>
       </c>
       <c r="D29">
-        <v>-5.390810542450943</v>
+        <v>-3.695016210317476</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -797,13 +797,13 @@
         <v>28</v>
       </c>
       <c r="B30">
-        <v>51.52333333333333</v>
+        <v>35.85333333333333</v>
       </c>
       <c r="C30">
-        <v>47.25395316825139</v>
+        <v>40.43817042050289</v>
       </c>
       <c r="D30">
-        <v>4.269380165081941</v>
+        <v>-4.584837087169561</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -811,13 +811,13 @@
         <v>29</v>
       </c>
       <c r="B31">
-        <v>45.57666666666666</v>
+        <v>51.52333333333333</v>
       </c>
       <c r="C31">
-        <v>42.02945757236483</v>
+        <v>48.11310723473277</v>
       </c>
       <c r="D31">
-        <v>3.547209094301834</v>
+        <v>3.41022609860056</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -825,13 +825,13 @@
         <v>30</v>
       </c>
       <c r="B32">
-        <v>43.92666666666667</v>
+        <v>45.57666666666666</v>
       </c>
       <c r="C32">
-        <v>49.73438536976187</v>
+        <v>41.75525112964709</v>
       </c>
       <c r="D32">
-        <v>-5.807718703095205</v>
+        <v>3.821415537019575</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -839,13 +839,13 @@
         <v>31</v>
       </c>
       <c r="B33">
-        <v>95.08999999999999</v>
+        <v>43.92666666666667</v>
       </c>
       <c r="C33">
-        <v>93.70755564338582</v>
+        <v>48.29348493963783</v>
       </c>
       <c r="D33">
-        <v>1.382444356614172</v>
+        <v>-4.366818272971159</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -853,13 +853,13 @@
         <v>32</v>
       </c>
       <c r="B34">
-        <v>98.63</v>
+        <v>95.08999999999999</v>
       </c>
       <c r="C34">
-        <v>95.92792492017725</v>
+        <v>92.60193296069673</v>
       </c>
       <c r="D34">
-        <v>2.702075079822748</v>
+        <v>2.48806703930326</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -867,13 +867,13 @@
         <v>33</v>
       </c>
       <c r="B35">
-        <v>102.7266666666667</v>
+        <v>102.47</v>
       </c>
       <c r="C35">
-        <v>97.02287832402492</v>
+        <v>99.18463296449649</v>
       </c>
       <c r="D35">
-        <v>5.703788342641758</v>
+        <v>3.285367035503512</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -881,13 +881,13 @@
         <v>34</v>
       </c>
       <c r="B36">
-        <v>100.3466666666666</v>
+        <v>102.7266666666667</v>
       </c>
       <c r="C36">
-        <v>96.06895133501392</v>
+        <v>93.1959946831203</v>
       </c>
       <c r="D36">
-        <v>4.277715331652729</v>
+        <v>9.53067198354637</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -895,13 +895,13 @@
         <v>35</v>
       </c>
       <c r="B37">
-        <v>96.90666666666668</v>
+        <v>100.3466666666666</v>
       </c>
       <c r="C37">
-        <v>95.64483506746664</v>
+        <v>94.12109306213654</v>
       </c>
       <c r="D37">
-        <v>1.261831599200036</v>
+        <v>6.225573604530112</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -909,13 +909,13 @@
         <v>36</v>
       </c>
       <c r="B38">
-        <v>77.96000000000001</v>
+        <v>96.90666666666668</v>
       </c>
       <c r="C38">
-        <v>92.9057171525404</v>
+        <v>92.86504941064914</v>
       </c>
       <c r="D38">
-        <v>-14.9457171525404</v>
+        <v>4.041617256017545</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -923,13 +923,13 @@
         <v>37</v>
       </c>
       <c r="B39">
-        <v>34.64333333333334</v>
+        <v>77.96000000000001</v>
       </c>
       <c r="C39">
-        <v>34.62718071485236</v>
+        <v>92.37779511139337</v>
       </c>
       <c r="D39">
-        <v>0.01615261848098015</v>
+        <v>-14.41779511139336</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -937,13 +937,13 @@
         <v>38</v>
       </c>
       <c r="B40">
-        <v>12.78666666666667</v>
+        <v>34.64333333333334</v>
       </c>
       <c r="C40">
-        <v>13.5423160151553</v>
+        <v>35.01726310044067</v>
       </c>
       <c r="D40">
-        <v>-0.75564934848863</v>
+        <v>-0.3739297671073274</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -951,13 +951,13 @@
         <v>39</v>
       </c>
       <c r="B41">
-        <v>11.54333333333333</v>
+        <v>12.78666666666667</v>
       </c>
       <c r="C41">
-        <v>12.93682797878173</v>
+        <v>13.65029123446729</v>
       </c>
       <c r="D41">
-        <v>-1.393494645448399</v>
+        <v>-0.8636245678006187</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -965,13 +965,13 @@
         <v>40</v>
       </c>
       <c r="B42">
-        <v>11.31</v>
+        <v>11.54333333333333</v>
       </c>
       <c r="C42">
-        <v>12.91347081432671</v>
+        <v>12.89324156599896</v>
       </c>
       <c r="D42">
-        <v>-1.603470814326716</v>
+        <v>-1.349908232665621</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -979,13 +979,13 @@
         <v>41</v>
       </c>
       <c r="B43">
-        <v>5</v>
+        <v>11.31</v>
       </c>
       <c r="C43">
-        <v>8.432644297678539</v>
+        <v>13.09004864703666</v>
       </c>
       <c r="D43">
-        <v>-3.432644297678539</v>
+        <v>-1.78004864703666</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -993,13 +993,13 @@
         <v>42</v>
       </c>
       <c r="B44">
-        <v>15.03</v>
+        <v>5</v>
       </c>
       <c r="C44">
-        <v>10.37571174939164</v>
+        <v>8.403990263537059</v>
       </c>
       <c r="D44">
-        <v>4.654288250608362</v>
+        <v>-3.403990263537059</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1007,13 +1007,13 @@
         <v>43</v>
       </c>
       <c r="B45">
-        <v>11.5</v>
+        <v>15.03</v>
       </c>
       <c r="C45">
-        <v>9.256895082277047</v>
+        <v>11.46211629323005</v>
       </c>
       <c r="D45">
-        <v>2.243104917722953</v>
+        <v>3.567883706769951</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1021,13 +1021,13 @@
         <v>44</v>
       </c>
       <c r="B46">
-        <v>12.72</v>
+        <v>11.5</v>
       </c>
       <c r="C46">
-        <v>14.06330619559888</v>
+        <v>8.99174248838769</v>
       </c>
       <c r="D46">
-        <v>-1.343306195598881</v>
+        <v>2.50825751161231</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1035,13 +1035,13 @@
         <v>45</v>
       </c>
       <c r="B47">
-        <v>45.75666666666666</v>
+        <v>12.72</v>
       </c>
       <c r="C47">
-        <v>44.39273938989947</v>
+        <v>14.37733793257433</v>
       </c>
       <c r="D47">
-        <v>1.363927276767193</v>
+        <v>-1.657337932574331</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1049,13 +1049,13 @@
         <v>46</v>
       </c>
       <c r="B48">
-        <v>81.90000000000001</v>
+        <v>45.75666666666666</v>
       </c>
       <c r="C48">
-        <v>82.29356267376143</v>
+        <v>43.92940399150011</v>
       </c>
       <c r="D48">
-        <v>-0.3935626737614228</v>
+        <v>1.827262675166551</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1063,13 +1063,13 @@
         <v>47</v>
       </c>
       <c r="B49">
-        <v>64.62666666666667</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="C49">
-        <v>75.20318342592596</v>
+        <v>82.63824084193585</v>
       </c>
       <c r="D49">
-        <v>-10.57651675925929</v>
+        <v>-0.7382408419358484</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1077,13 +1077,13 @@
         <v>48</v>
       </c>
       <c r="B50">
-        <v>62.52666666666666</v>
+        <v>64.62666666666667</v>
       </c>
       <c r="C50">
-        <v>76.55102131817256</v>
+        <v>75.44784560323937</v>
       </c>
       <c r="D50">
-        <v>-14.0243546515059</v>
+        <v>-10.82117893657271</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1091,13 +1091,13 @@
         <v>49</v>
       </c>
       <c r="B51">
-        <v>47.15333333333334</v>
+        <v>62.52666666666666</v>
       </c>
       <c r="C51">
-        <v>48.68033602326416</v>
+        <v>76.59071583273209</v>
       </c>
       <c r="D51">
-        <v>-1.527002689930825</v>
+        <v>-14.06404916606542</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1105,13 +1105,13 @@
         <v>50</v>
       </c>
       <c r="B52">
-        <v>45.83666666666667</v>
+        <v>47.15333333333334</v>
       </c>
       <c r="C52">
-        <v>51.11007067132551</v>
+        <v>48.73196473485758</v>
       </c>
       <c r="D52">
-        <v>-5.273404004658843</v>
+        <v>-1.578631401524241</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1119,13 +1119,13 @@
         <v>51</v>
       </c>
       <c r="B53">
-        <v>38.355</v>
+        <v>45.83666666666667</v>
       </c>
       <c r="C53">
-        <v>41.43588126808975</v>
+        <v>50.16681757155851</v>
       </c>
       <c r="D53">
-        <v>-3.080881268089747</v>
+        <v>-4.330150904891845</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1133,13 +1133,13 @@
         <v>52</v>
       </c>
       <c r="B54">
-        <v>44.71333333333334</v>
+        <v>38.355</v>
       </c>
       <c r="C54">
-        <v>42.71765154184232</v>
+        <v>40.67141589549592</v>
       </c>
       <c r="D54">
-        <v>1.995681791491023</v>
+        <v>-2.316415895495915</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1147,13 +1147,13 @@
         <v>53</v>
       </c>
       <c r="B55">
-        <v>47.76</v>
+        <v>44.71333333333334</v>
       </c>
       <c r="C55">
-        <v>42.87849997392937</v>
+        <v>41.11357922649679</v>
       </c>
       <c r="D55">
-        <v>4.881500026070633</v>
+        <v>3.599754106836549</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1161,13 +1161,13 @@
         <v>54</v>
       </c>
       <c r="B56">
-        <v>39.245</v>
+        <v>47.76</v>
       </c>
       <c r="C56">
-        <v>44.07520420650183</v>
+        <v>42.23516105766668</v>
       </c>
       <c r="D56">
-        <v>-4.830204206501833</v>
+        <v>5.524838942333318</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1175,13 +1175,13 @@
         <v>55</v>
       </c>
       <c r="B57">
-        <v>77.61499999999999</v>
+        <v>39.245</v>
       </c>
       <c r="C57">
-        <v>78.02790066646315</v>
+        <v>43.84508679551087</v>
       </c>
       <c r="D57">
-        <v>-0.4129006664631589</v>
+        <v>-4.600086795510869</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1189,13 +1189,13 @@
         <v>56</v>
       </c>
       <c r="B58">
-        <v>103.49</v>
+        <v>77.61499999999999</v>
       </c>
       <c r="C58">
-        <v>101.0073528211881</v>
+        <v>77.97924296356419</v>
       </c>
       <c r="D58">
-        <v>2.482647178811959</v>
+        <v>-0.3642429635641946</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1203,13 +1203,13 @@
         <v>57</v>
       </c>
       <c r="B59">
-        <v>113.4033333333334</v>
+        <v>103.49</v>
       </c>
       <c r="C59">
-        <v>106.4670987903596</v>
+        <v>101.15885051338</v>
       </c>
       <c r="D59">
-        <v>6.936234542973793</v>
+        <v>2.331149486620006</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1217,13 +1217,13 @@
         <v>58</v>
       </c>
       <c r="B60">
-        <v>111.1766666666667</v>
+        <v>105.84</v>
       </c>
       <c r="C60">
-        <v>107.2088073733876</v>
+        <v>91.92837323131197</v>
       </c>
       <c r="D60">
-        <v>3.967859293279048</v>
+        <v>13.91162676868804</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1231,13 +1231,13 @@
         <v>59</v>
       </c>
       <c r="B61">
-        <v>96.82333333333334</v>
+        <v>111.1766666666667</v>
       </c>
       <c r="C61">
-        <v>102.4428461068429</v>
+        <v>104.1382977159129</v>
       </c>
       <c r="D61">
-        <v>-5.619512773509513</v>
+        <v>7.038368950753807</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1245,13 +1245,13 @@
         <v>60</v>
       </c>
       <c r="B62">
-        <v>97.61666666666667</v>
+        <v>96.82333333333334</v>
       </c>
       <c r="C62">
-        <v>101.8222326768879</v>
+        <v>99.99333843742184</v>
       </c>
       <c r="D62">
-        <v>-4.205566010221176</v>
+        <v>-3.170005104088503</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -1259,13 +1259,13 @@
         <v>61</v>
       </c>
       <c r="B63">
-        <v>56.66999999999999</v>
+        <v>97.61666666666667</v>
       </c>
       <c r="C63">
-        <v>58.2359914021164</v>
+        <v>103.9217451448241</v>
       </c>
       <c r="D63">
-        <v>-1.565991402116403</v>
+        <v>-6.305078478157398</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1273,13 +1273,13 @@
         <v>62</v>
       </c>
       <c r="B64">
-        <v>6.97</v>
+        <v>56.66999999999999</v>
       </c>
       <c r="C64">
-        <v>7.674700735150553</v>
+        <v>58.49395351851854</v>
       </c>
       <c r="D64">
-        <v>-0.7047007351505536</v>
+        <v>-1.823953518518543</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1287,13 +1287,13 @@
         <v>63</v>
       </c>
       <c r="B65">
-        <v>10.31666666666667</v>
+        <v>6.97</v>
       </c>
       <c r="C65">
-        <v>12.60295992244095</v>
+        <v>7.355361139294771</v>
       </c>
       <c r="D65">
-        <v>-2.286293255774281</v>
+        <v>-0.3853611392947709</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1301,13 +1301,13 @@
         <v>64</v>
       </c>
       <c r="B66">
-        <v>8.77</v>
+        <v>10.31666666666667</v>
       </c>
       <c r="C66">
-        <v>9.773840810324009</v>
+        <v>12.0615829717352</v>
       </c>
       <c r="D66">
-        <v>-1.003840810324009</v>
+        <v>-1.744916305068534</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1315,13 +1315,13 @@
         <v>65</v>
       </c>
       <c r="B67">
-        <v>5</v>
+        <v>8.77</v>
       </c>
       <c r="C67">
-        <v>10.36403445411533</v>
+        <v>10.08375893804316</v>
       </c>
       <c r="D67">
-        <v>-5.36403445411533</v>
+        <v>-1.313758938043156</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1329,13 +1329,13 @@
         <v>66</v>
       </c>
       <c r="B68">
-        <v>10.83333333333333</v>
+        <v>5</v>
       </c>
       <c r="C68">
-        <v>10.51910397434052</v>
+        <v>10.71864772784</v>
       </c>
       <c r="D68">
-        <v>0.3142293589928133</v>
+        <v>-5.718647727840004</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1343,13 +1343,13 @@
         <v>67</v>
       </c>
       <c r="B69">
-        <v>11.64</v>
+        <v>11.77</v>
       </c>
       <c r="C69">
-        <v>8.612101607634189</v>
+        <v>10.68086735026555</v>
       </c>
       <c r="D69">
-        <v>3.027898392365811</v>
+        <v>1.089132649734454</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1360,10 +1360,10 @@
         <v>12.24</v>
       </c>
       <c r="C70">
-        <v>12.04690458120045</v>
+        <v>11.65329642133235</v>
       </c>
       <c r="D70">
-        <v>0.1930954187995511</v>
+        <v>0.5867035786676524</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1374,10 +1374,10 @@
         <v>44.71333333333334</v>
       </c>
       <c r="C71">
-        <v>44.62249219566567</v>
+        <v>45.61227709509724</v>
       </c>
       <c r="D71">
-        <v>0.09084113766766677</v>
+        <v>-0.8989437617639027</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1388,10 +1388,10 @@
         <v>82.36</v>
       </c>
       <c r="C72">
-        <v>81.16332224460723</v>
+        <v>77.9284454100529</v>
       </c>
       <c r="D72">
-        <v>1.19667775539277</v>
+        <v>4.431554589947098</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1402,10 +1402,10 @@
         <v>92</v>
       </c>
       <c r="C73">
-        <v>84.28614327799214</v>
+        <v>89.57848306115186</v>
       </c>
       <c r="D73">
-        <v>7.713856722007861</v>
+        <v>2.421516938848143</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -1416,10 +1416,10 @@
         <v>71.5</v>
       </c>
       <c r="C74">
-        <v>76.46842701384965</v>
+        <v>80.80646735750362</v>
       </c>
       <c r="D74">
-        <v>-4.968427013849649</v>
+        <v>-9.306467357503621</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -1430,10 +1430,10 @@
         <v>44.31666666666666</v>
       </c>
       <c r="C75">
-        <v>44.6213557240781</v>
+        <v>44.62717962015576</v>
       </c>
       <c r="D75">
-        <v>-0.3046890574114371</v>
+        <v>-0.3105129534890949</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -1444,10 +1444,10 @@
         <v>48.035</v>
       </c>
       <c r="C76">
-        <v>46.5738868246582</v>
+        <v>47.29656541575284</v>
       </c>
       <c r="D76">
-        <v>1.461113175341794</v>
+        <v>0.7384345842471589</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -1458,10 +1458,10 @@
         <v>41.56</v>
       </c>
       <c r="C77">
-        <v>44.782941432861</v>
+        <v>44.6950878755929</v>
       </c>
       <c r="D77">
-        <v>-3.222941432860999</v>
+        <v>-3.135087875592895</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -1472,10 +1472,10 @@
         <v>27.79333333333333</v>
       </c>
       <c r="C78">
-        <v>34.55605885476206</v>
+        <v>32.70824263743177</v>
       </c>
       <c r="D78">
-        <v>-6.762725521428724</v>
+        <v>-4.914909304098433</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -1486,10 +1486,10 @@
         <v>44.33000000000001</v>
       </c>
       <c r="C79">
-        <v>42.9243728733815</v>
+        <v>42.51645025069845</v>
       </c>
       <c r="D79">
-        <v>1.405627126618505</v>
+        <v>1.813549749301551</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -1500,10 +1500,10 @@
         <v>24.57666666666666</v>
       </c>
       <c r="C80">
-        <v>37.74371551671047</v>
+        <v>38.88258577509704</v>
       </c>
       <c r="D80">
-        <v>-13.1670488500438</v>
+        <v>-14.30591910843038</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -1514,10 +1514,10 @@
         <v>109.17</v>
       </c>
       <c r="C81">
-        <v>107.7346572151805</v>
+        <v>107.7361975075626</v>
       </c>
       <c r="D81">
-        <v>1.435342784819497</v>
+        <v>1.433802492437408</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -1528,10 +1528,10 @@
         <v>99.75333333333333</v>
       </c>
       <c r="C82">
-        <v>96.82543024450855</v>
+        <v>95.72042826077185</v>
       </c>
       <c r="D82">
-        <v>2.927903088824777</v>
+        <v>4.032905072561476</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -1542,10 +1542,10 @@
         <v>106.1166666666667</v>
       </c>
       <c r="C83">
-        <v>106.3414629987704</v>
+        <v>105.830282107378</v>
       </c>
       <c r="D83">
-        <v>-0.2247963321036792</v>
+        <v>0.2863845592887202</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -1556,10 +1556,10 @@
         <v>107.85</v>
       </c>
       <c r="C84">
-        <v>104.5696338532876</v>
+        <v>102.8807237274937</v>
       </c>
       <c r="D84">
-        <v>3.280366146712424</v>
+        <v>4.969276272506335</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -1570,10 +1570,10 @@
         <v>106.6533333333334</v>
       </c>
       <c r="C85">
-        <v>103.1588620878227</v>
+        <v>102.6431249928102</v>
       </c>
       <c r="D85">
-        <v>3.494471245510681</v>
+        <v>4.010208340523178</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -1584,10 +1584,10 @@
         <v>94.98333333333335</v>
       </c>
       <c r="C86">
-        <v>97.8379636993181</v>
+        <v>98.44589428952469</v>
       </c>
       <c r="D86">
-        <v>-2.854630365984747</v>
+        <v>-3.462560956191339</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -1598,10 +1598,10 @@
         <v>24.66666666666667</v>
       </c>
       <c r="C87">
-        <v>26.62611514824327</v>
+        <v>27.4013563095238</v>
       </c>
       <c r="D87">
-        <v>-1.959448481576604</v>
+        <v>-2.734689642857134</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -1612,10 +1612,10 @@
         <v>13.06</v>
       </c>
       <c r="C88">
-        <v>13.5527422638902</v>
+        <v>13.77086575298757</v>
       </c>
       <c r="D88">
-        <v>-0.4927422638902019</v>
+        <v>-0.710865752987571</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -1626,10 +1626,10 @@
         <v>7.223333333333333</v>
       </c>
       <c r="C89">
-        <v>8.894659546832132</v>
+        <v>9.780271817462868</v>
       </c>
       <c r="D89">
-        <v>-1.6713262134988</v>
+        <v>-2.556938484129535</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -1637,13 +1637,13 @@
         <v>88</v>
       </c>
       <c r="B90">
-        <v>12.58666666666667</v>
+        <v>11.715</v>
       </c>
       <c r="C90">
-        <v>11.63605042212424</v>
+        <v>11.30472750736453</v>
       </c>
       <c r="D90">
-        <v>0.950616244542422</v>
+        <v>0.4102724926354657</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -1654,10 +1654,10 @@
         <v>8.004999999999999</v>
       </c>
       <c r="C91">
-        <v>11.28565300504265</v>
+        <v>9.622770039042642</v>
       </c>
       <c r="D91">
-        <v>-3.280653005042655</v>
+        <v>-1.617770039042643</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -1668,10 +1668,10 @@
         <v>12.54</v>
       </c>
       <c r="C92">
-        <v>10.8091626512639</v>
+        <v>12.91209088708487</v>
       </c>
       <c r="D92">
-        <v>1.730837348736102</v>
+        <v>-0.3720908870848749</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -1682,10 +1682,10 @@
         <v>10.88</v>
       </c>
       <c r="C93">
-        <v>10.16449374323653</v>
+        <v>9.617120328669142</v>
       </c>
       <c r="D93">
-        <v>0.715506256763474</v>
+        <v>1.262879671330859</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -1696,10 +1696,10 @@
         <v>48.94</v>
       </c>
       <c r="C94">
-        <v>49.2780441796418</v>
+        <v>47.96350933461736</v>
       </c>
       <c r="D94">
-        <v>-0.3380441796417983</v>
+        <v>0.9764906653826344</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -1710,10 +1710,10 @@
         <v>66.90666666666667</v>
       </c>
       <c r="C95">
-        <v>62.362813531746</v>
+        <v>63.18753863095237</v>
       </c>
       <c r="D95">
-        <v>4.543853134920667</v>
+        <v>3.719128035714299</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -1724,10 +1724,10 @@
         <v>77.68333333333334</v>
       </c>
       <c r="C96">
-        <v>76.44945996501592</v>
+        <v>73.46163167455364</v>
       </c>
       <c r="D96">
-        <v>1.233873368317418</v>
+        <v>4.221701658779693</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -1738,10 +1738,10 @@
         <v>61.97</v>
       </c>
       <c r="C97">
-        <v>72.67964918662761</v>
+        <v>71.84885213360711</v>
       </c>
       <c r="D97">
-        <v>-10.70964918662762</v>
+        <v>-9.878852133607111</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -1752,10 +1752,10 @@
         <v>41.26666666666667</v>
       </c>
       <c r="C98">
-        <v>41.51592799226555</v>
+        <v>42.2884231571348</v>
       </c>
       <c r="D98">
-        <v>-0.24926132559888</v>
+        <v>-1.021756490468128</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -1766,10 +1766,10 @@
         <v>33.96</v>
       </c>
       <c r="C99">
-        <v>39.26035034232557</v>
+        <v>40.50294054893634</v>
       </c>
       <c r="D99">
-        <v>-5.300350342325565</v>
+        <v>-6.542940548936336</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -1780,10 +1780,10 @@
         <v>45.59</v>
       </c>
       <c r="C100">
-        <v>40.42786103451065</v>
+        <v>40.49050481499156</v>
       </c>
       <c r="D100">
-        <v>5.162138965489348</v>
+        <v>5.099495185008436</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -1794,10 +1794,10 @@
         <v>41.73333333333333</v>
       </c>
       <c r="C101">
-        <v>39.29550410624613</v>
+        <v>38.89377131010029</v>
       </c>
       <c r="D101">
-        <v>2.437829227087192</v>
+        <v>2.839562023233036</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -1808,10 +1808,10 @@
         <v>39.79333333333333</v>
       </c>
       <c r="C102">
-        <v>42.90478528864392</v>
+        <v>42.95416176922439</v>
       </c>
       <c r="D102">
-        <v>-3.111451955310592</v>
+        <v>-3.160828435891062</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -1822,10 +1822,10 @@
         <v>38.09</v>
       </c>
       <c r="C103">
-        <v>39.66926531844066</v>
+        <v>36.61176488671753</v>
       </c>
       <c r="D103">
-        <v>-1.579265318440655</v>
+        <v>1.478235113282473</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -1836,10 +1836,10 @@
         <v>110.95</v>
       </c>
       <c r="C104">
-        <v>107.7463922436196</v>
+        <v>108.9091941746864</v>
       </c>
       <c r="D104">
-        <v>3.203607756380379</v>
+        <v>2.040805825313598</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -1850,10 +1850,10 @@
         <v>87.47333333333334</v>
       </c>
       <c r="C105">
-        <v>95.10845725674108</v>
+        <v>94.1821988105674</v>
       </c>
       <c r="D105">
-        <v>-7.635123923407733</v>
+        <v>-6.708865477234056</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -1864,10 +1864,10 @@
         <v>122.9233333333333</v>
       </c>
       <c r="C106">
-        <v>117.7739403127003</v>
+        <v>116.2554522051593</v>
       </c>
       <c r="D106">
-        <v>5.149393020633056</v>
+        <v>6.667881128173988</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -1878,10 +1878,10 @@
         <v>95.8</v>
       </c>
       <c r="C107">
-        <v>100.5374880438301</v>
+        <v>101.8269871044465</v>
       </c>
       <c r="D107">
-        <v>-4.737488043830069</v>
+        <v>-6.026987104446548</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -1892,10 +1892,10 @@
         <v>83.69</v>
       </c>
       <c r="C108">
-        <v>110.7173840219932</v>
+        <v>109.789099668218</v>
       </c>
       <c r="D108">
-        <v>-27.02738402199323</v>
+        <v>-26.09909966821797</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -1906,10 +1906,10 @@
         <v>94.98333333333333</v>
       </c>
       <c r="C109">
-        <v>99.6215985065827</v>
+        <v>95.16988464336117</v>
       </c>
       <c r="D109">
-        <v>-4.638265173249366</v>
+        <v>-0.1865513100278378</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -1920,10 +1920,10 @@
         <v>42.99333333333333</v>
       </c>
       <c r="C110">
-        <v>43.49920332662255</v>
+        <v>43.97616307791998</v>
       </c>
       <c r="D110">
-        <v>-0.5058699932892168</v>
+        <v>-0.9828297445866525</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -1934,10 +1934,10 @@
         <v>13.05</v>
       </c>
       <c r="C111">
-        <v>15.11110463955026</v>
+        <v>15.28153257275132</v>
       </c>
       <c r="D111">
-        <v>-2.06110463955026</v>
+        <v>-2.231532572751323</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -1948,10 +1948,10 @@
         <v>11.355</v>
       </c>
       <c r="C112">
-        <v>13.61191372500459</v>
+        <v>13.133498716791</v>
       </c>
       <c r="D112">
-        <v>-2.256913725004594</v>
+        <v>-1.778498716791004</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -1962,10 +1962,10 @@
         <v>7.865</v>
       </c>
       <c r="C113">
-        <v>12.20077669573204</v>
+        <v>11.89913184537475</v>
       </c>
       <c r="D113">
-        <v>-4.335776695732038</v>
+        <v>-4.034131845374747</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -1976,10 +1976,10 @@
         <v>20.8</v>
       </c>
       <c r="C114">
-        <v>12.78806176688186</v>
+        <v>12.24918919596358</v>
       </c>
       <c r="D114">
-        <v>8.011938233118141</v>
+        <v>8.550810804036418</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -1990,10 +1990,10 @@
         <v>15.07</v>
       </c>
       <c r="C115">
-        <v>8.949013233710687</v>
+        <v>9.87656823111322</v>
       </c>
       <c r="D115">
-        <v>6.120986766289313</v>
+        <v>5.19343176888678</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2004,10 +2004,10 @@
         <v>13.37</v>
       </c>
       <c r="C116">
-        <v>15.47329526398587</v>
+        <v>15.0328537933852</v>
       </c>
       <c r="D116">
-        <v>-2.103295263985871</v>
+        <v>-1.662853793385201</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2018,10 +2018,10 @@
         <v>5</v>
       </c>
       <c r="C117">
-        <v>10.65624006615372</v>
+        <v>10.99657516631982</v>
       </c>
       <c r="D117">
-        <v>-5.656240066153716</v>
+        <v>-5.99657516631982</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2032,10 +2032,10 @@
         <v>56.01666666666667</v>
       </c>
       <c r="C118">
-        <v>49.27699899295996</v>
+        <v>46.98933076912856</v>
       </c>
       <c r="D118">
-        <v>6.739667673706712</v>
+        <v>9.027335897538116</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2046,10 +2046,10 @@
         <v>83.76666666666667</v>
       </c>
       <c r="C119">
-        <v>82.50888055074557</v>
+        <v>82.51159591570467</v>
       </c>
       <c r="D119">
-        <v>1.257786115921093</v>
+        <v>1.255070750961991</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2060,10 +2060,10 @@
         <v>91.16000000000001</v>
       </c>
       <c r="C120">
-        <v>80.34971414682541</v>
+        <v>81.39542562169309</v>
       </c>
       <c r="D120">
-        <v>10.81028585317461</v>
+        <v>9.764574378306918</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2074,10 +2074,10 @@
         <v>77.76333333333334</v>
       </c>
       <c r="C121">
-        <v>79.15974109126982</v>
+        <v>80.77335510582012</v>
       </c>
       <c r="D121">
-        <v>-1.396407757936487</v>
+        <v>-3.01002177248678</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2088,10 +2088,10 @@
         <v>52.68666666666667</v>
       </c>
       <c r="C122">
-        <v>52.52974469049468</v>
+        <v>52.12278630078896</v>
       </c>
       <c r="D122">
-        <v>0.1569219761719864</v>
+        <v>0.5638803658777078</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2102,10 +2102,10 @@
         <v>49.035</v>
       </c>
       <c r="C123">
-        <v>50.16289393979976</v>
+        <v>50.61835621254308</v>
       </c>
       <c r="D123">
-        <v>-1.127893939799762</v>
+        <v>-1.58335621254308</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2116,10 +2116,10 @@
         <v>51.41666666666666</v>
       </c>
       <c r="C124">
-        <v>51.69049541932292</v>
+        <v>51.95496494440314</v>
       </c>
       <c r="D124">
-        <v>-0.2738287526562573</v>
+        <v>-0.5382982777364802</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2130,10 +2130,10 @@
         <v>34.825</v>
       </c>
       <c r="C125">
-        <v>42.3540772105764</v>
+        <v>43.45566442706556</v>
       </c>
       <c r="D125">
-        <v>-7.529077210576396</v>
+        <v>-8.630664427065561</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2141,13 +2141,13 @@
         <v>124</v>
       </c>
       <c r="B126">
-        <v>47.08666666666667</v>
+        <v>24.83</v>
       </c>
       <c r="C126">
-        <v>46.55577179853834</v>
+        <v>45.76900919091735</v>
       </c>
       <c r="D126">
-        <v>0.5308948681283283</v>
+        <v>-20.93900919091735</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -2158,10 +2158,10 @@
         <v>50.48</v>
       </c>
       <c r="C127">
-        <v>44.00623729125875</v>
+        <v>45.14450628078496</v>
       </c>
       <c r="D127">
-        <v>6.473762708741255</v>
+        <v>5.335493719215044</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -2172,10 +2172,10 @@
         <v>132.0533333333333</v>
       </c>
       <c r="C128">
-        <v>128.1387608419565</v>
+        <v>128.2149537602213</v>
       </c>
       <c r="D128">
-        <v>3.914572491376788</v>
+        <v>3.838379573112036</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -2186,10 +2186,10 @@
         <v>127.3333333333333</v>
       </c>
       <c r="C129">
-        <v>105.869038842292</v>
+        <v>105.3978247284197</v>
       </c>
       <c r="D129">
-        <v>21.46429449104133</v>
+        <v>21.93550860491361</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -2200,10 +2200,10 @@
         <v>129.7166666666667</v>
       </c>
       <c r="C130">
-        <v>128.9820241071428</v>
+        <v>127.6512758348596</v>
       </c>
       <c r="D130">
-        <v>0.7346425595238202</v>
+        <v>2.065390831807022</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -2214,10 +2214,10 @@
         <v>123.6133333333333</v>
       </c>
       <c r="C131">
-        <v>121.5786499214483</v>
+        <v>123.3303027726903</v>
       </c>
       <c r="D131">
-        <v>2.034683411884998</v>
+        <v>0.2830305606430841</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -2228,10 +2228,10 @@
         <v>107.4733333333333</v>
       </c>
       <c r="C132">
-        <v>121.8448196345131</v>
+        <v>119.3838262925827</v>
       </c>
       <c r="D132">
-        <v>-14.3714863011798</v>
+        <v>-11.91049295924937</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -2242,10 +2242,10 @@
         <v>122.82</v>
       </c>
       <c r="C133">
-        <v>123.3699825534416</v>
+        <v>118.1312375850402</v>
       </c>
       <c r="D133">
-        <v>-0.5499825534415805</v>
+        <v>4.688762414959825</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -2256,10 +2256,10 @@
         <v>28.82666666666667</v>
       </c>
       <c r="C134">
-        <v>29.70849796817332</v>
+        <v>30.03311621151995</v>
       </c>
       <c r="D134">
-        <v>-0.8818313015066543</v>
+        <v>-1.206449544853285</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -2270,10 +2270,10 @@
         <v>19.38</v>
       </c>
       <c r="C135">
-        <v>17.94748742063492</v>
+        <v>17.93288356661857</v>
       </c>
       <c r="D135">
-        <v>1.432512579365078</v>
+        <v>1.447116433381428</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -2284,10 +2284,10 @@
         <v>13.52666666666667</v>
       </c>
       <c r="C136">
-        <v>14.91354648997686</v>
+        <v>14.26210311373811</v>
       </c>
       <c r="D136">
-        <v>-1.386879823310197</v>
+        <v>-0.7354364470714483</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -2298,10 +2298,10 @@
         <v>11.08666666666667</v>
       </c>
       <c r="C137">
-        <v>13.00531111700009</v>
+        <v>13.23096331221172</v>
       </c>
       <c r="D137">
-        <v>-1.918644450333426</v>
+        <v>-2.144296645545055</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -2312,10 +2312,10 @@
         <v>14.46333333333333</v>
       </c>
       <c r="C138">
-        <v>13.62523296986132</v>
+        <v>13.33633593225787</v>
       </c>
       <c r="D138">
-        <v>0.8381003634720177</v>
+        <v>1.126997401075458</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -2326,10 +2326,10 @@
         <v>12.43333333333333</v>
       </c>
       <c r="C139">
-        <v>12.30523265229926</v>
+        <v>12.38095382091979</v>
       </c>
       <c r="D139">
-        <v>0.1281006810340699</v>
+        <v>0.05237951241353755</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -2340,10 +2340,10 @@
         <v>11.88</v>
       </c>
       <c r="C140">
-        <v>13.53173005864441</v>
+        <v>13.44837834337252</v>
       </c>
       <c r="D140">
-        <v>-1.651730058644413</v>
+        <v>-1.568378343372517</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -2354,10 +2354,10 @@
         <v>19.56</v>
       </c>
       <c r="C141">
-        <v>15.92665020649624</v>
+        <v>15.68924720760909</v>
       </c>
       <c r="D141">
-        <v>3.633349793503765</v>
+        <v>3.870752792390917</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -2365,13 +2365,13 @@
         <v>140</v>
       </c>
       <c r="B142">
-        <v>60.12</v>
+        <v>53.43</v>
       </c>
       <c r="C142">
-        <v>54.88531990417447</v>
+        <v>51.32431112932361</v>
       </c>
       <c r="D142">
-        <v>5.234680095825532</v>
+        <v>2.105688870676389</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -2379,13 +2379,13 @@
         <v>141</v>
       </c>
       <c r="B143">
-        <v>89.20666666666666</v>
+        <v>85.16</v>
       </c>
       <c r="C143">
-        <v>88.845728452381</v>
+        <v>80.71308619708994</v>
       </c>
       <c r="D143">
-        <v>0.3609382142856674</v>
+        <v>4.446913802910061</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -2396,10 +2396,10 @@
         <v>87.38666666666667</v>
       </c>
       <c r="C144">
-        <v>84.91477578042326</v>
+        <v>81.20841468253965</v>
       </c>
       <c r="D144">
-        <v>2.471890886243415</v>
+        <v>6.178251984127016</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -2410,10 +2410,10 @@
         <v>71.26333333333334</v>
       </c>
       <c r="C145">
-        <v>78.90253941798943</v>
+        <v>79.42913373316499</v>
       </c>
       <c r="D145">
-        <v>-7.639206084656095</v>
+        <v>-8.165800399831653</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -2424,10 +2424,10 @@
         <v>60.665</v>
       </c>
       <c r="C146">
-        <v>58.3975720887446</v>
+        <v>58.5928488425926</v>
       </c>
       <c r="D146">
-        <v>2.267427911255396</v>
+        <v>2.072151157407397</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -2438,10 +2438,10 @@
         <v>47.01</v>
       </c>
       <c r="C147">
-        <v>48.51200158029158</v>
+        <v>49.2020307283241</v>
       </c>
       <c r="D147">
-        <v>-1.502001580291584</v>
+        <v>-2.192030728324106</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -2452,10 +2452,10 @@
         <v>42.40666666666667</v>
       </c>
       <c r="C148">
-        <v>48.17899609455169</v>
+        <v>46.15664032887811</v>
       </c>
       <c r="D148">
-        <v>-5.772329427885019</v>
+        <v>-3.749973662211445</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -2466,10 +2466,10 @@
         <v>51.97</v>
       </c>
       <c r="C149">
-        <v>51.67167594643995</v>
+        <v>51.09932749102689</v>
       </c>
       <c r="D149">
-        <v>0.2983240535600444</v>
+        <v>0.870672508973108</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -2480,10 +2480,10 @@
         <v>46.59</v>
       </c>
       <c r="C150">
-        <v>45.44447007116104</v>
+        <v>46.52433716043234</v>
       </c>
       <c r="D150">
-        <v>1.145529928838961</v>
+        <v>0.06566283956766483</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -2494,10 +2494,10 @@
         <v>47</v>
       </c>
       <c r="C151">
-        <v>51.55962314412928</v>
+        <v>51.09072824385307</v>
       </c>
       <c r="D151">
-        <v>-4.559623144129276</v>
+        <v>-4.090728243853071</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -2505,13 +2505,13 @@
         <v>150</v>
       </c>
       <c r="B152">
-        <v>120.3433333333333</v>
+        <v>120.745</v>
       </c>
       <c r="C152">
-        <v>118.4900677762321</v>
+        <v>119.0327165559305</v>
       </c>
       <c r="D152">
-        <v>1.853265557101182</v>
+        <v>1.712283444069513</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -2522,10 +2522,10 @@
         <v>113.56</v>
       </c>
       <c r="C153">
-        <v>107.7847421332435</v>
+        <v>107.151422659901</v>
       </c>
       <c r="D153">
-        <v>5.775257866756547</v>
+        <v>6.408577340099001</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -2536,10 +2536,10 @@
         <v>118.7433333333333</v>
       </c>
       <c r="C154">
-        <v>118.9286461658819</v>
+        <v>118.2373314911157</v>
       </c>
       <c r="D154">
-        <v>-0.1853128325485329</v>
+        <v>0.5060018422176853</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -2550,10 +2550,10 @@
         <v>94.68333333333334</v>
       </c>
       <c r="C155">
-        <v>109.8011242203914</v>
+        <v>109.5707795070057</v>
       </c>
       <c r="D155">
-        <v>-15.11779088705811</v>
+        <v>-14.88744617367239</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -2564,10 +2564,10 @@
         <v>102.745</v>
       </c>
       <c r="C156">
-        <v>114.6697528520562</v>
+        <v>115.8069935888221</v>
       </c>
       <c r="D156">
-        <v>-11.92475285205622</v>
+        <v>-13.06199358882211</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -2575,13 +2575,13 @@
         <v>155</v>
       </c>
       <c r="B157">
-        <v>140.325</v>
+        <v>149.53</v>
       </c>
       <c r="C157">
-        <v>126.5466432284382</v>
+        <v>130.9632722817461</v>
       </c>
       <c r="D157">
-        <v>13.77835677156179</v>
+        <v>18.5667277182539</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -2592,10 +2592,10 @@
         <v>56.585</v>
       </c>
       <c r="C158">
-        <v>57.61276529100529</v>
+        <v>58.02433251322753</v>
       </c>
       <c r="D158">
-        <v>-1.027765291005288</v>
+        <v>-1.439332513227527</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -2606,10 +2606,10 @@
         <v>7.59</v>
       </c>
       <c r="C159">
-        <v>8.274720994253331</v>
+        <v>8.864815763045048</v>
       </c>
       <c r="D159">
-        <v>-0.6847209942533308</v>
+        <v>-1.274815763045048</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -2620,10 +2620,10 @@
         <v>7.546666666666667</v>
       </c>
       <c r="C160">
-        <v>10.83226897442369</v>
+        <v>11.64885711087243</v>
       </c>
       <c r="D160">
-        <v>-3.285602307757021</v>
+        <v>-4.10219044420576</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -2634,10 +2634,10 @@
         <v>15.1</v>
       </c>
       <c r="C161">
-        <v>10.4873261874037</v>
+        <v>11.48261840864489</v>
       </c>
       <c r="D161">
-        <v>4.6126738125963</v>
+        <v>3.617381591355109</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -2648,10 +2648,10 @@
         <v>9.58</v>
       </c>
       <c r="C162">
-        <v>8.742968104432737</v>
+        <v>9.334375081252643</v>
       </c>
       <c r="D162">
-        <v>0.8370318955672627</v>
+        <v>0.2456249187473567</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -2662,10 +2662,10 @@
         <v>13.825</v>
       </c>
       <c r="C163">
-        <v>11.78865355456323</v>
+        <v>12.54442743420294</v>
       </c>
       <c r="D163">
-        <v>2.036346445436772</v>
+        <v>1.280572565797064</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -2676,10 +2676,10 @@
         <v>18.45</v>
       </c>
       <c r="C164">
-        <v>10.52265392281176</v>
+        <v>11.01111455934081</v>
       </c>
       <c r="D164">
-        <v>7.927346077188243</v>
+        <v>7.438885440659186</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -2690,10 +2690,10 @@
         <v>11.41333333333333</v>
       </c>
       <c r="C165">
-        <v>13.80451282479687</v>
+        <v>13.44208149222374</v>
       </c>
       <c r="D165">
-        <v>-2.391179491463534</v>
+        <v>-2.028748158890405</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -2704,10 +2704,10 @@
         <v>53.755</v>
       </c>
       <c r="C166">
-        <v>50.82060677683977</v>
+        <v>54.57132909946949</v>
       </c>
       <c r="D166">
-        <v>2.934393223160228</v>
+        <v>-0.8163290994694989</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -2718,10 +2718,10 @@
         <v>79.09</v>
       </c>
       <c r="C167">
-        <v>79.75208786517132</v>
+        <v>79.02143421916047</v>
       </c>
       <c r="D167">
-        <v>-0.6620878651713156</v>
+        <v>0.0685657808395348</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -2732,10 +2732,10 @@
         <v>82.60333333333334</v>
       </c>
       <c r="C168">
-        <v>81.07073680735931</v>
+        <v>79.89339738576241</v>
       </c>
       <c r="D168">
-        <v>1.532596525974029</v>
+        <v>2.709935947570926</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -2746,10 +2746,10 @@
         <v>64.60000000000001</v>
       </c>
       <c r="C169">
-        <v>76.07815107804234</v>
+        <v>74.89064797619049</v>
       </c>
       <c r="D169">
-        <v>-11.47815107804233</v>
+        <v>-10.29064797619048</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -2760,10 +2760,10 @@
         <v>28.6</v>
       </c>
       <c r="C170">
-        <v>28.58243159031484</v>
+        <v>28.8168946279707</v>
       </c>
       <c r="D170">
-        <v>0.01756840968516471</v>
+        <v>-0.2168946279706994</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -2774,10 +2774,10 @@
         <v>34.175</v>
       </c>
       <c r="C171">
-        <v>42.99806935657595</v>
+        <v>39.58327928943599</v>
       </c>
       <c r="D171">
-        <v>-8.823069356575957</v>
+        <v>-5.408279289435988</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -2788,10 +2788,10 @@
         <v>34.14</v>
       </c>
       <c r="C172">
-        <v>30.83896427560424</v>
+        <v>30.3079555442328</v>
       </c>
       <c r="D172">
-        <v>3.301035724395756</v>
+        <v>3.832044455767196</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -2802,10 +2802,10 @@
         <v>57.43</v>
       </c>
       <c r="C173">
-        <v>43.2629264226684</v>
+        <v>47.29266084057669</v>
       </c>
       <c r="D173">
-        <v>14.1670735773316</v>
+        <v>10.13733915942331</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -2816,10 +2816,10 @@
         <v>39.425</v>
       </c>
       <c r="C174">
-        <v>41.61674825051915</v>
+        <v>42.65765788426931</v>
       </c>
       <c r="D174">
-        <v>-2.191748250519154</v>
+        <v>-3.232657884269315</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -2830,10 +2830,10 @@
         <v>42.16666666666666</v>
       </c>
       <c r="C175">
-        <v>53.43038229602594</v>
+        <v>53.72611138812609</v>
       </c>
       <c r="D175">
-        <v>-11.26371562935928</v>
+        <v>-11.55944472145943</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -2844,10 +2844,10 @@
         <v>106.81</v>
       </c>
       <c r="C176">
-        <v>106.2981820902206</v>
+        <v>106.5162529304401</v>
       </c>
       <c r="D176">
-        <v>0.511817909779424</v>
+        <v>0.2937470695599131</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -2858,10 +2858,10 @@
         <v>114.185</v>
       </c>
       <c r="C177">
-        <v>106.0790474811947</v>
+        <v>104.7500266553817</v>
       </c>
       <c r="D177">
-        <v>8.105952518805282</v>
+        <v>9.434973344618285</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -2872,10 +2872,10 @@
         <v>118.87</v>
       </c>
       <c r="C178">
-        <v>113.9510540390951</v>
+        <v>111.0204865677061</v>
       </c>
       <c r="D178">
-        <v>4.918945960904935</v>
+        <v>7.849513432293904</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -2886,10 +2886,10 @@
         <v>96.91333333333334</v>
       </c>
       <c r="C179">
-        <v>107.2787124225341</v>
+        <v>106.7215484746367</v>
       </c>
       <c r="D179">
-        <v>-10.36537908920076</v>
+        <v>-9.808215141303364</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -2900,10 +2900,10 @@
         <v>117.6333333333333</v>
       </c>
       <c r="C180">
-        <v>112.8411962421539</v>
+        <v>110.7782500530408</v>
       </c>
       <c r="D180">
-        <v>4.79213709117947</v>
+        <v>6.855083280292533</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -2914,10 +2914,10 @@
         <v>103.68</v>
       </c>
       <c r="C181">
-        <v>106.6611214486185</v>
+        <v>103.1068512014723</v>
       </c>
       <c r="D181">
-        <v>-2.981121448618538</v>
+        <v>0.5731487985276829</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -2928,10 +2928,10 @@
         <v>34.13333333333333</v>
       </c>
       <c r="C182">
-        <v>33.99230749335165</v>
+        <v>34.46618624744961</v>
       </c>
       <c r="D182">
-        <v>0.1410258399816868</v>
+        <v>-0.3328529141162733</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -2942,10 +2942,10 @@
         <v>18.29</v>
       </c>
       <c r="C183">
-        <v>19.06536188492064</v>
+        <v>18.81468864417989</v>
       </c>
       <c r="D183">
-        <v>-0.7753618849206383</v>
+        <v>-0.5246886441798928</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -2956,10 +2956,10 @@
         <v>10.3</v>
       </c>
       <c r="C184">
-        <v>10.73733502466819</v>
+        <v>10.49456936054183</v>
       </c>
       <c r="D184">
-        <v>-0.4373350246681866</v>
+        <v>-0.1945693605418306</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -2970,10 +2970,10 @@
         <v>8.443333333333333</v>
       </c>
       <c r="C185">
-        <v>10.9697162191367</v>
+        <v>11.00571386426244</v>
       </c>
       <c r="D185">
-        <v>-2.526382885803368</v>
+        <v>-2.562380530929108</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -2984,10 +2984,10 @@
         <v>21.08</v>
       </c>
       <c r="C186">
-        <v>11.66428856187834</v>
+        <v>11.58344670937913</v>
       </c>
       <c r="D186">
-        <v>9.41571143812166</v>
+        <v>9.496553290620872</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -2998,10 +2998,10 @@
         <v>10.56333333333333</v>
       </c>
       <c r="C187">
-        <v>8.769405370423478</v>
+        <v>9.122921861138739</v>
       </c>
       <c r="D187">
-        <v>1.793927962909855</v>
+        <v>1.440411472194594</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -3012,10 +3012,10 @@
         <v>13.15</v>
       </c>
       <c r="C188">
-        <v>13.23830075703796</v>
+        <v>13.24301777051568</v>
       </c>
       <c r="D188">
-        <v>-0.0883007570379597</v>
+        <v>-0.09301777051568294</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -3026,10 +3026,10 @@
         <v>5</v>
       </c>
       <c r="C189">
-        <v>6.576708965190258</v>
+        <v>7.046738981957078</v>
       </c>
       <c r="D189">
-        <v>-1.576708965190258</v>
+        <v>-2.046738981957078</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -3040,10 +3040,10 @@
         <v>38.52</v>
       </c>
       <c r="C190">
-        <v>38.23253475733939</v>
+        <v>38.09673782617502</v>
       </c>
       <c r="D190">
-        <v>0.2874652426606161</v>
+        <v>0.4232621738249804</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -3054,10 +3054,10 @@
         <v>64.71666666666667</v>
       </c>
       <c r="C191">
-        <v>65.44840505291005</v>
+        <v>65.69584989417989</v>
       </c>
       <c r="D191">
-        <v>-0.7317383862433786</v>
+        <v>-0.979183227513218</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -3068,10 +3068,10 @@
         <v>76.65666666666665</v>
       </c>
       <c r="C192">
-        <v>76.02727265091389</v>
+        <v>76.3993826761202</v>
       </c>
       <c r="D192">
-        <v>0.6293940157527658</v>
+        <v>0.2572839905464548</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -3082,10 +3082,10 @@
         <v>80.24333333333333</v>
       </c>
       <c r="C193">
-        <v>70.99156535917786</v>
+        <v>72.71127990218115</v>
       </c>
       <c r="D193">
-        <v>9.25176797415547</v>
+        <v>7.532053431152178</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -3096,10 +3096,10 @@
         <v>46.72</v>
       </c>
       <c r="C194">
-        <v>47.09892481424848</v>
+        <v>47.31199174867498</v>
       </c>
       <c r="D194">
-        <v>-0.378924814248478</v>
+        <v>-0.5919917486749853</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -3110,10 +3110,10 @@
         <v>36.95666666666667</v>
       </c>
       <c r="C195">
-        <v>40.07663382677716</v>
+        <v>40.59815440710907</v>
       </c>
       <c r="D195">
-        <v>-3.119967160110491</v>
+        <v>-3.6414877404424</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -3124,10 +3124,10 @@
         <v>42.045</v>
       </c>
       <c r="C196">
-        <v>42.11436723066939</v>
+        <v>42.6342036834115</v>
       </c>
       <c r="D196">
-        <v>-0.06936723066938555</v>
+        <v>-0.5892036834114975</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -3138,10 +3138,10 @@
         <v>39.57333333333333</v>
       </c>
       <c r="C197">
-        <v>38.65246125272321</v>
+        <v>36.21943089197558</v>
       </c>
       <c r="D197">
-        <v>0.9208720806101169</v>
+        <v>3.353902441357747</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -3152,10 +3152,10 @@
         <v>38.76</v>
       </c>
       <c r="C198">
-        <v>40.67842294795111</v>
+        <v>38.24814036745245</v>
       </c>
       <c r="D198">
-        <v>-1.918422947951107</v>
+        <v>0.511859632547548</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -3166,10 +3166,10 @@
         <v>32.405</v>
       </c>
       <c r="C199">
-        <v>37.6035021047401</v>
+        <v>37.53389284757866</v>
       </c>
       <c r="D199">
-        <v>-5.198502104740101</v>
+        <v>-5.128892847578662</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -3180,10 +3180,10 @@
         <v>104.0866666666667</v>
       </c>
       <c r="C200">
-        <v>103.1284812613775</v>
+        <v>103.6209635196929</v>
       </c>
       <c r="D200">
-        <v>0.958185405289143</v>
+        <v>0.4657031469737376</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -3194,10 +3194,10 @@
         <v>100.1366666666667</v>
       </c>
       <c r="C201">
-        <v>94.84613167634654</v>
+        <v>96.4732073998114</v>
       </c>
       <c r="D201">
-        <v>5.290534990320111</v>
+        <v>3.663459266855256</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -3208,10 +3208,10 @@
         <v>106.3433333333333</v>
       </c>
       <c r="C202">
-        <v>104.3402437686717</v>
+        <v>103.3020913842695</v>
       </c>
       <c r="D202">
-        <v>2.003089564661607</v>
+        <v>3.041241949063846</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -3222,10 +3222,10 @@
         <v>85.98666666666666</v>
       </c>
       <c r="C203">
-        <v>96.50450086009852</v>
+        <v>96.35530347893271</v>
       </c>
       <c r="D203">
-        <v>-10.51783419343185</v>
+        <v>-10.36863681226605</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -3236,10 +3236,10 @@
         <v>111.8533333333333</v>
       </c>
       <c r="C204">
-        <v>107.5127483329493</v>
+        <v>106.586175158455</v>
       </c>
       <c r="D204">
-        <v>4.34058500038401</v>
+        <v>5.26715817487829</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -3250,10 +3250,10 @@
         <v>69.36</v>
       </c>
       <c r="C205">
-        <v>94.64261755188339</v>
+        <v>92.27433170832418</v>
       </c>
       <c r="D205">
-        <v>-25.28261755188339</v>
+        <v>-22.91433170832418</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -3264,10 +3264,10 @@
         <v>48.50333333333333</v>
       </c>
       <c r="C206">
-        <v>48.56445006619651</v>
+        <v>48.26024537616132</v>
       </c>
       <c r="D206">
-        <v>-0.06111673286317654</v>
+        <v>0.2430879571720084</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -3278,10 +3278,10 @@
         <v>9.890000000000001</v>
       </c>
       <c r="C207">
-        <v>10.80987847460846</v>
+        <v>10.89022469038131</v>
       </c>
       <c r="D207">
-        <v>-0.9198784746084581</v>
+        <v>-1.000224690381307</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -3292,10 +3292,10 @@
         <v>10.32</v>
       </c>
       <c r="C208">
-        <v>12.42950241215389</v>
+        <v>13.0667838633285</v>
       </c>
       <c r="D208">
-        <v>-2.109502412153891</v>
+        <v>-2.746783863328504</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -3306,10 +3306,10 @@
         <v>8.49</v>
       </c>
       <c r="C209">
-        <v>9.609344545960402</v>
+        <v>10.26155434588871</v>
       </c>
       <c r="D209">
-        <v>-1.119344545960402</v>
+        <v>-1.771554345888708</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -3320,10 +3320,10 @@
         <v>16.1</v>
       </c>
       <c r="C210">
-        <v>10.87211447849758</v>
+        <v>10.75466729579239</v>
       </c>
       <c r="D210">
-        <v>5.227885521502419</v>
+        <v>5.34533270420761</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -3334,10 +3334,10 @@
         <v>11.705</v>
       </c>
       <c r="C211">
-        <v>10.08829178053792</v>
+        <v>9.242832137773151</v>
       </c>
       <c r="D211">
-        <v>1.616708219462081</v>
+        <v>2.462167862226849</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -3348,10 +3348,10 @@
         <v>15.54666666666667</v>
       </c>
       <c r="C212">
-        <v>14.31585570285568</v>
+        <v>14.63413680102748</v>
       </c>
       <c r="D212">
-        <v>1.230810963810987</v>
+        <v>0.9125298656391845</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -3362,10 +3362,10 @@
         <v>8.35</v>
       </c>
       <c r="C213">
-        <v>10.56477251683729</v>
+        <v>10.34411606080917</v>
       </c>
       <c r="D213">
-        <v>-2.214772516837291</v>
+        <v>-1.994116060809166</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -3376,10 +3376,10 @@
         <v>45.26</v>
       </c>
       <c r="C214">
-        <v>45.19136577889785</v>
+        <v>44.95983853761605</v>
       </c>
       <c r="D214">
-        <v>0.06863422110214401</v>
+        <v>0.3001614623839473</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -3390,10 +3390,10 @@
         <v>71.31666666666666</v>
       </c>
       <c r="C215">
-        <v>72.85232363095241</v>
+        <v>72.08254945767192</v>
       </c>
       <c r="D215">
-        <v>-1.535656964285749</v>
+        <v>-0.7658827910052537</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -3404,10 +3404,10 @@
         <v>67.47333333333334</v>
       </c>
       <c r="C216">
-        <v>71.91985828042326</v>
+        <v>71.54614773809517</v>
       </c>
       <c r="D216">
-        <v>-4.446524947089912</v>
+        <v>-4.072814404761829</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -3418,10 +3418,10 @@
         <v>73.48</v>
       </c>
       <c r="C217">
-        <v>71.87616439356937</v>
+        <v>70.51158681216931</v>
       </c>
       <c r="D217">
-        <v>1.603835606430636</v>
+        <v>2.968413187830691</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -3432,10 +3432,10 @@
         <v>36.7</v>
       </c>
       <c r="C218">
-        <v>37.39384611061431</v>
+        <v>36.22829064453565</v>
       </c>
       <c r="D218">
-        <v>-0.6938461106143095</v>
+        <v>0.4717093554643412</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -3446,10 +3446,10 @@
         <v>34.59</v>
       </c>
       <c r="C219">
-        <v>40.81697344879755</v>
+        <v>42.32939840056838</v>
       </c>
       <c r="D219">
-        <v>-6.226973448797551</v>
+        <v>-7.739398400568376</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -3460,10 +3460,10 @@
         <v>52.96</v>
       </c>
       <c r="C220">
-        <v>42.44670028500675</v>
+        <v>43.71558033716512</v>
       </c>
       <c r="D220">
-        <v>10.51329971499325</v>
+        <v>9.244419662834879</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -3474,10 +3474,10 @@
         <v>39.97</v>
       </c>
       <c r="C221">
-        <v>38.94001821066325</v>
+        <v>38.51240669286116</v>
       </c>
       <c r="D221">
-        <v>1.029981789336752</v>
+        <v>1.457593307138836</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -3485,13 +3485,13 @@
         <v>220</v>
       </c>
       <c r="B222">
-        <v>32.71666666666667</v>
+        <v>29.915</v>
       </c>
       <c r="C222">
-        <v>43.0172956288821</v>
+        <v>42.54982392674363</v>
       </c>
       <c r="D222">
-        <v>-10.30062896221543</v>
+        <v>-12.63482392674363</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -3502,10 +3502,10 @@
         <v>35.26</v>
       </c>
       <c r="C223">
-        <v>38.49270625176677</v>
+        <v>38.46071667584745</v>
       </c>
       <c r="D223">
-        <v>-3.232706251766771</v>
+        <v>-3.200716675847453</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -3513,13 +3513,13 @@
         <v>222</v>
       </c>
       <c r="B224">
-        <v>89.68333333333334</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="C224">
-        <v>88.81718993386245</v>
+        <v>98.24619108872606</v>
       </c>
       <c r="D224">
-        <v>0.8661433994708858</v>
+        <v>0.9038089112739414</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -3530,10 +3530,10 @@
         <v>119.5033333333333</v>
       </c>
       <c r="C225">
-        <v>115.7639842593682</v>
+        <v>114.3631337861105</v>
       </c>
       <c r="D225">
-        <v>3.739349073965087</v>
+        <v>5.140199547222807</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -3541,13 +3541,13 @@
         <v>224</v>
       </c>
       <c r="B226">
-        <v>92.83999999999999</v>
+        <v>102.53</v>
       </c>
       <c r="C226">
-        <v>104.4729484785065</v>
+        <v>104.8895919671802</v>
       </c>
       <c r="D226">
-        <v>-11.63294847850649</v>
+        <v>-2.359591967180179</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -3558,10 +3558,10 @@
         <v>87.22666666666667</v>
       </c>
       <c r="C227">
-        <v>112.1601273796449</v>
+        <v>110.6300617294089</v>
       </c>
       <c r="D227">
-        <v>-24.93346071297827</v>
+        <v>-23.40339506274226</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -3569,13 +3569,13 @@
         <v>226</v>
       </c>
       <c r="B228">
-        <v>95.42666666666666</v>
+        <v>96.905</v>
       </c>
       <c r="C228">
-        <v>98.678961834118</v>
+        <v>100.0074155684485</v>
       </c>
       <c r="D228">
-        <v>-3.252295167451337</v>
+        <v>-3.10241556844845</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -3586,10 +3586,10 @@
         <v>114.475</v>
       </c>
       <c r="C229">
-        <v>105.3817379850551</v>
+        <v>102.2277208081583</v>
       </c>
       <c r="D229">
-        <v>9.093262014944941</v>
+        <v>12.24727919184167</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -3600,10 +3600,10 @@
         <v>47.77666666666666</v>
       </c>
       <c r="C230">
-        <v>48.61921004039385</v>
+        <v>48.31293449176246</v>
       </c>
       <c r="D230">
-        <v>-0.8425433737271817</v>
+        <v>-0.5362678250957984</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -3614,10 +3614,10 @@
         <v>11.06</v>
       </c>
       <c r="C231">
-        <v>11.81698084412813</v>
+        <v>11.61297217511821</v>
       </c>
       <c r="D231">
-        <v>-0.7569808441281314</v>
+        <v>-0.5529721751182102</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -3628,10 +3628,10 @@
         <v>14.19</v>
       </c>
       <c r="C232">
-        <v>12.5207087469302</v>
+        <v>12.90750698576993</v>
       </c>
       <c r="D232">
-        <v>1.669291253069801</v>
+        <v>1.282493014230074</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -3639,13 +3639,13 @@
         <v>231</v>
       </c>
       <c r="B233">
-        <v>8.885</v>
+        <v>6.52</v>
       </c>
       <c r="C233">
-        <v>9.611266988338164</v>
+        <v>8.284593406694171</v>
       </c>
       <c r="D233">
-        <v>-0.7262669883381641</v>
+        <v>-1.764593406694171</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -3656,10 +3656,10 @@
         <v>10.64</v>
       </c>
       <c r="C234">
-        <v>11.21301152470471</v>
+        <v>10.82264131253901</v>
       </c>
       <c r="D234">
-        <v>-0.573011524704711</v>
+        <v>-0.1826413125390118</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -3670,10 +3670,10 @@
         <v>6.23</v>
       </c>
       <c r="C235">
-        <v>9.281476694337504</v>
+        <v>9.064190965281012</v>
       </c>
       <c r="D235">
-        <v>-3.051476694337504</v>
+        <v>-2.834190965281012</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -3684,10 +3684,10 @@
         <v>17.995</v>
       </c>
       <c r="C236">
-        <v>11.54878739101828</v>
+        <v>11.71302532933893</v>
       </c>
       <c r="D236">
-        <v>6.446212608981725</v>
+        <v>6.281974670661072</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -3698,10 +3698,10 @@
         <v>18.07</v>
       </c>
       <c r="C237">
-        <v>8.296402637890253</v>
+        <v>7.772937384328558</v>
       </c>
       <c r="D237">
-        <v>9.773597362109747</v>
+        <v>10.29706261567144</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -3709,13 +3709,13 @@
         <v>236</v>
       </c>
       <c r="B238">
-        <v>42.03</v>
+        <v>51.01000000000001</v>
       </c>
       <c r="C238">
-        <v>39.70439278125568</v>
+        <v>46.53830625218681</v>
       </c>
       <c r="D238">
-        <v>2.325607218744317</v>
+        <v>4.471693747813191</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -3726,10 +3726,10 @@
         <v>72.26333333333334</v>
       </c>
       <c r="C239">
-        <v>73.05019418650794</v>
+        <v>72.20398302248675</v>
       </c>
       <c r="D239">
-        <v>-0.786860853174602</v>
+        <v>0.05935031084658249</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -3740,10 +3740,10 @@
         <v>72.03</v>
       </c>
       <c r="C240">
-        <v>72.89809966269841</v>
+        <v>71.27734857142855</v>
       </c>
       <c r="D240">
-        <v>-0.8680996626984125</v>
+        <v>0.7526514285714541</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -3754,10 +3754,10 @@
         <v>65.89</v>
       </c>
       <c r="C241">
-        <v>71.29884720899469</v>
+        <v>70.70895051587303</v>
       </c>
       <c r="D241">
-        <v>-5.408847208994686</v>
+        <v>-4.818950515873027</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -3768,10 +3768,10 @@
         <v>42.73333333333333</v>
       </c>
       <c r="C242">
-        <v>43.22364183290858</v>
+        <v>43.5362820810449</v>
       </c>
       <c r="D242">
-        <v>-0.4903084995752494</v>
+        <v>-0.802948747711568</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -3782,10 +3782,10 @@
         <v>51.35333333333333</v>
       </c>
       <c r="C243">
-        <v>48.63845049993891</v>
+        <v>49.22160399387008</v>
       </c>
       <c r="D243">
-        <v>2.714882833394427</v>
+        <v>2.131729339463256</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -3796,10 +3796,10 @@
         <v>54.04</v>
       </c>
       <c r="C244">
-        <v>44.52512332267226</v>
+        <v>44.86329912598737</v>
       </c>
       <c r="D244">
-        <v>9.514876677327734</v>
+        <v>9.176700874012624</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -3810,10 +3810,10 @@
         <v>34.57666666666667</v>
       </c>
       <c r="C245">
-        <v>39.85738447680232</v>
+        <v>40.48125608412519</v>
       </c>
       <c r="D245">
-        <v>-5.280717810135648</v>
+        <v>-5.904589417458524</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -3824,10 +3824,10 @@
         <v>40.555</v>
       </c>
       <c r="C246">
-        <v>48.37172653459427</v>
+        <v>48.69101070686702</v>
       </c>
       <c r="D246">
-        <v>-7.816726534594274</v>
+        <v>-8.136010706867019</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -3838,10 +3838,10 @@
         <v>33.225</v>
       </c>
       <c r="C247">
-        <v>39.00106452053452</v>
+        <v>37.34509227875171</v>
       </c>
       <c r="D247">
-        <v>-5.776064520534518</v>
+        <v>-4.120092278751713</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -3849,13 +3849,13 @@
         <v>246</v>
       </c>
       <c r="B248">
-        <v>112.61</v>
+        <v>107.875</v>
       </c>
       <c r="C248">
-        <v>111.0949156110824</v>
+        <v>107.3574394028749</v>
       </c>
       <c r="D248">
-        <v>1.515084388917643</v>
+        <v>0.5175605971250974</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -3866,10 +3866,10 @@
         <v>103.24</v>
       </c>
       <c r="C249">
-        <v>101.4874598408275</v>
+        <v>91.20975967273957</v>
       </c>
       <c r="D249">
-        <v>1.752540159172455</v>
+        <v>12.03024032726043</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -3880,10 +3880,10 @@
         <v>91.66000000000001</v>
       </c>
       <c r="C250">
-        <v>107.0309053174728</v>
+        <v>102.124325107528</v>
       </c>
       <c r="D250">
-        <v>-15.37090531747275</v>
+        <v>-10.46432510752801</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -3894,10 +3894,10 @@
         <v>111.79</v>
       </c>
       <c r="C251">
-        <v>107.1670145201408</v>
+        <v>108.3715094652924</v>
       </c>
       <c r="D251">
-        <v>4.622985479859167</v>
+        <v>3.41849053470763</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -3908,10 +3908,10 @@
         <v>95.55</v>
       </c>
       <c r="C252">
-        <v>100.5173298940583</v>
+        <v>97.44116088234703</v>
       </c>
       <c r="D252">
-        <v>-4.967329894058295</v>
+        <v>-1.891160882347037</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -3922,10 +3922,10 @@
         <v>87.67333333333333</v>
       </c>
       <c r="C253">
-        <v>102.2062669183738</v>
+        <v>101.2402275229772</v>
       </c>
       <c r="D253">
-        <v>-14.53293358504047</v>
+        <v>-13.56689418964382</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -3936,10 +3936,10 @@
         <v>36.795</v>
       </c>
       <c r="C254">
-        <v>36.84613875881904</v>
+        <v>36.60691012024348</v>
       </c>
       <c r="D254">
-        <v>-0.05113875881904306</v>
+        <v>0.1880898797565251</v>
       </c>
     </row>
   </sheetData>
